--- a/docentes/Vargas Olvera Francisco Eduardo - Estadisticos 20212.xlsx
+++ b/docentes/Vargas Olvera Francisco Eduardo - Estadisticos 20212.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="190" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="340" uniqueCount="160">
   <si>
     <t>Mat</t>
   </si>
@@ -145,6 +145,75 @@
     <t>XOTLANIHUA</t>
   </si>
   <si>
+    <t>ANDRADE</t>
+  </si>
+  <si>
+    <t>ANTONIO</t>
+  </si>
+  <si>
+    <t>ARROYO</t>
+  </si>
+  <si>
+    <t>BASILIO</t>
+  </si>
+  <si>
+    <t>BUSTOS</t>
+  </si>
+  <si>
+    <t>DEMUNER</t>
+  </si>
+  <si>
+    <t>GASCA</t>
+  </si>
+  <si>
+    <t>GUERRA</t>
+  </si>
+  <si>
+    <t>HUESCA</t>
+  </si>
+  <si>
+    <t>LORENZO</t>
+  </si>
+  <si>
+    <t>LOBATO</t>
+  </si>
+  <si>
+    <t>MATA</t>
+  </si>
+  <si>
+    <t>PARRA</t>
+  </si>
+  <si>
+    <t>RIVERA</t>
+  </si>
+  <si>
+    <t>RICO</t>
+  </si>
+  <si>
+    <t>TORRES</t>
+  </si>
+  <si>
+    <t>VAZQUEZ</t>
+  </si>
+  <si>
+    <t>VELAZQEZ</t>
+  </si>
+  <si>
+    <t>XOCUA</t>
+  </si>
+  <si>
+    <t>ZUÑIGA</t>
+  </si>
+  <si>
+    <t>APALE</t>
+  </si>
+  <si>
+    <t>GAMEZ</t>
+  </si>
+  <si>
+    <t>ROMERO</t>
+  </si>
+  <si>
     <t>CIRUELO</t>
   </si>
   <si>
@@ -172,9 +241,6 @@
     <t>ENRIQUEZ</t>
   </si>
   <si>
-    <t>LORENZO</t>
-  </si>
-  <si>
     <t>SANTES</t>
   </si>
   <si>
@@ -190,9 +256,6 @@
     <t>OFICIAL</t>
   </si>
   <si>
-    <t>ANTONIO</t>
-  </si>
-  <si>
     <t>PEREZ</t>
   </si>
   <si>
@@ -205,6 +268,69 @@
     <t>TETLA</t>
   </si>
   <si>
+    <t>MONTALVO</t>
+  </si>
+  <si>
+    <t>ESTEVEZ</t>
+  </si>
+  <si>
+    <t>ORTIZ</t>
+  </si>
+  <si>
+    <t>MENDOZA</t>
+  </si>
+  <si>
+    <t>CERON</t>
+  </si>
+  <si>
+    <t>RUIZ</t>
+  </si>
+  <si>
+    <t>ALONSO</t>
+  </si>
+  <si>
+    <t>JERONIMO</t>
+  </si>
+  <si>
+    <t>DOMINGUEZ</t>
+  </si>
+  <si>
+    <t>MIXCOA</t>
+  </si>
+  <si>
+    <t>CANSECO</t>
+  </si>
+  <si>
+    <t>SARMIENTO</t>
+  </si>
+  <si>
+    <t>AGUILAR</t>
+  </si>
+  <si>
+    <t>BAUTISTA</t>
+  </si>
+  <si>
+    <t>RODRIGUEZ</t>
+  </si>
+  <si>
+    <t>MELO</t>
+  </si>
+  <si>
+    <t>VICTORIANO</t>
+  </si>
+  <si>
+    <t>ZEPAHUA</t>
+  </si>
+  <si>
+    <t>ROBLES</t>
+  </si>
+  <si>
+    <t>SILVERIO</t>
+  </si>
+  <si>
+    <t>CASTILLO</t>
+  </si>
+  <si>
     <t>FATIMA</t>
   </si>
   <si>
@@ -284,6 +410,93 @@
   </si>
   <si>
     <t>ERIKA</t>
+  </si>
+  <si>
+    <t>PATRICIA</t>
+  </si>
+  <si>
+    <t>LUIS YAEL</t>
+  </si>
+  <si>
+    <t>VICTOR HUGO</t>
+  </si>
+  <si>
+    <t>VANESA</t>
+  </si>
+  <si>
+    <t>SARAHI</t>
+  </si>
+  <si>
+    <t>ADRIANA ARELY</t>
+  </si>
+  <si>
+    <t>ARANTXA</t>
+  </si>
+  <si>
+    <t>MARIA YAZMIN</t>
+  </si>
+  <si>
+    <t>JAEL SAMAI</t>
+  </si>
+  <si>
+    <t>LIZBET</t>
+  </si>
+  <si>
+    <t>XIMENA</t>
+  </si>
+  <si>
+    <t>ALDAIR OMAR</t>
+  </si>
+  <si>
+    <t>GUADALUPE</t>
+  </si>
+  <si>
+    <t>DANIELA RUBI</t>
+  </si>
+  <si>
+    <t>CRISTIAN ARTURO</t>
+  </si>
+  <si>
+    <t>SUEMI</t>
+  </si>
+  <si>
+    <t>ESTHER ARISBETH</t>
+  </si>
+  <si>
+    <t>JAROMI YAJAIRA</t>
+  </si>
+  <si>
+    <t>EDGAR RAMSES</t>
+  </si>
+  <si>
+    <t>BERENICE</t>
+  </si>
+  <si>
+    <t>IRIS VIANNEY</t>
+  </si>
+  <si>
+    <t>MARIAN</t>
+  </si>
+  <si>
+    <t>PAULINA</t>
+  </si>
+  <si>
+    <t>AYARI</t>
+  </si>
+  <si>
+    <t>DANIELA</t>
+  </si>
+  <si>
+    <t>JOSE MIGUEL</t>
+  </si>
+  <si>
+    <t>MARCOS</t>
+  </si>
+  <si>
+    <t>ROGELIO</t>
+  </si>
+  <si>
+    <t>MICHELLE ROBERTA</t>
   </si>
 </sst>
 </file>
@@ -1034,7 +1247,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G28"/>
+  <dimension ref="A1:G58"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1072,10 +1285,10 @@
         <v>19</v>
       </c>
       <c r="C2" t="s">
-        <v>42</v>
+        <v>65</v>
       </c>
       <c r="D2" t="s">
-        <v>62</v>
+        <v>104</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1098,7 +1311,7 @@
         <v>27</v>
       </c>
       <c r="D3" t="s">
-        <v>63</v>
+        <v>105</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -1118,10 +1331,10 @@
         <v>21</v>
       </c>
       <c r="C4" t="s">
-        <v>43</v>
+        <v>66</v>
       </c>
       <c r="D4" t="s">
-        <v>64</v>
+        <v>106</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
@@ -1141,10 +1354,10 @@
         <v>22</v>
       </c>
       <c r="C5" t="s">
-        <v>44</v>
+        <v>67</v>
       </c>
       <c r="D5" t="s">
-        <v>65</v>
+        <v>107</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
@@ -1164,10 +1377,10 @@
         <v>23</v>
       </c>
       <c r="C6" t="s">
-        <v>45</v>
+        <v>68</v>
       </c>
       <c r="D6" t="s">
-        <v>66</v>
+        <v>108</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
@@ -1187,10 +1400,10 @@
         <v>24</v>
       </c>
       <c r="C7" t="s">
-        <v>46</v>
+        <v>69</v>
       </c>
       <c r="D7" t="s">
-        <v>67</v>
+        <v>109</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
@@ -1213,7 +1426,7 @@
         <v>23</v>
       </c>
       <c r="D8" t="s">
-        <v>68</v>
+        <v>110</v>
       </c>
       <c r="E8" t="s">
         <v>8</v>
@@ -1233,10 +1446,10 @@
         <v>26</v>
       </c>
       <c r="C9" t="s">
-        <v>47</v>
+        <v>70</v>
       </c>
       <c r="D9" t="s">
-        <v>69</v>
+        <v>111</v>
       </c>
       <c r="E9" t="s">
         <v>8</v>
@@ -1256,10 +1469,10 @@
         <v>27</v>
       </c>
       <c r="C10" t="s">
-        <v>48</v>
+        <v>71</v>
       </c>
       <c r="D10" t="s">
-        <v>70</v>
+        <v>112</v>
       </c>
       <c r="E10" t="s">
         <v>8</v>
@@ -1279,10 +1492,10 @@
         <v>27</v>
       </c>
       <c r="C11" t="s">
-        <v>49</v>
+        <v>72</v>
       </c>
       <c r="D11" t="s">
-        <v>71</v>
+        <v>113</v>
       </c>
       <c r="E11" t="s">
         <v>8</v>
@@ -1302,10 +1515,10 @@
         <v>28</v>
       </c>
       <c r="C12" t="s">
-        <v>50</v>
+        <v>73</v>
       </c>
       <c r="D12" t="s">
-        <v>72</v>
+        <v>114</v>
       </c>
       <c r="E12" t="s">
         <v>8</v>
@@ -1328,7 +1541,7 @@
         <v>51</v>
       </c>
       <c r="D13" t="s">
-        <v>73</v>
+        <v>115</v>
       </c>
       <c r="E13" t="s">
         <v>8</v>
@@ -1348,10 +1561,10 @@
         <v>30</v>
       </c>
       <c r="C14" t="s">
-        <v>52</v>
+        <v>74</v>
       </c>
       <c r="D14" t="s">
-        <v>74</v>
+        <v>116</v>
       </c>
       <c r="E14" t="s">
         <v>8</v>
@@ -1371,10 +1584,10 @@
         <v>31</v>
       </c>
       <c r="C15" t="s">
-        <v>53</v>
+        <v>75</v>
       </c>
       <c r="D15" t="s">
-        <v>75</v>
+        <v>117</v>
       </c>
       <c r="E15" t="s">
         <v>8</v>
@@ -1394,10 +1607,10 @@
         <v>32</v>
       </c>
       <c r="C16" t="s">
-        <v>54</v>
+        <v>76</v>
       </c>
       <c r="D16" t="s">
-        <v>76</v>
+        <v>118</v>
       </c>
       <c r="E16" t="s">
         <v>8</v>
@@ -1420,7 +1633,7 @@
         <v>22</v>
       </c>
       <c r="D17" t="s">
-        <v>77</v>
+        <v>119</v>
       </c>
       <c r="E17" t="s">
         <v>8</v>
@@ -1440,10 +1653,10 @@
         <v>32</v>
       </c>
       <c r="C18" t="s">
-        <v>55</v>
+        <v>77</v>
       </c>
       <c r="D18" t="s">
-        <v>78</v>
+        <v>120</v>
       </c>
       <c r="E18" t="s">
         <v>8</v>
@@ -1466,7 +1679,7 @@
         <v>25</v>
       </c>
       <c r="D19" t="s">
-        <v>79</v>
+        <v>121</v>
       </c>
       <c r="E19" t="s">
         <v>8</v>
@@ -1489,7 +1702,7 @@
         <v>51</v>
       </c>
       <c r="D20" t="s">
-        <v>80</v>
+        <v>122</v>
       </c>
       <c r="E20" t="s">
         <v>8</v>
@@ -1512,7 +1725,7 @@
         <v>28</v>
       </c>
       <c r="D21" t="s">
-        <v>81</v>
+        <v>123</v>
       </c>
       <c r="E21" t="s">
         <v>8</v>
@@ -1532,10 +1745,10 @@
         <v>36</v>
       </c>
       <c r="C22" t="s">
-        <v>56</v>
+        <v>78</v>
       </c>
       <c r="D22" t="s">
-        <v>82</v>
+        <v>124</v>
       </c>
       <c r="E22" t="s">
         <v>8</v>
@@ -1555,10 +1768,10 @@
         <v>37</v>
       </c>
       <c r="C23" t="s">
-        <v>57</v>
+        <v>43</v>
       </c>
       <c r="D23" t="s">
-        <v>83</v>
+        <v>125</v>
       </c>
       <c r="E23" t="s">
         <v>8</v>
@@ -1578,10 +1791,10 @@
         <v>38</v>
       </c>
       <c r="C24" t="s">
-        <v>58</v>
+        <v>79</v>
       </c>
       <c r="D24" t="s">
-        <v>84</v>
+        <v>126</v>
       </c>
       <c r="E24" t="s">
         <v>8</v>
@@ -1601,10 +1814,10 @@
         <v>38</v>
       </c>
       <c r="C25" t="s">
-        <v>59</v>
+        <v>80</v>
       </c>
       <c r="D25" t="s">
-        <v>85</v>
+        <v>127</v>
       </c>
       <c r="E25" t="s">
         <v>8</v>
@@ -1624,10 +1837,10 @@
         <v>39</v>
       </c>
       <c r="C26" t="s">
-        <v>60</v>
+        <v>81</v>
       </c>
       <c r="D26" t="s">
-        <v>86</v>
+        <v>128</v>
       </c>
       <c r="E26" t="s">
         <v>8</v>
@@ -1647,10 +1860,10 @@
         <v>40</v>
       </c>
       <c r="C27" t="s">
-        <v>61</v>
+        <v>82</v>
       </c>
       <c r="D27" t="s">
-        <v>87</v>
+        <v>129</v>
       </c>
       <c r="E27" t="s">
         <v>8</v>
@@ -1673,15 +1886,705 @@
         <v>41</v>
       </c>
       <c r="D28" t="s">
+        <v>130</v>
+      </c>
+      <c r="E28" t="s">
+        <v>8</v>
+      </c>
+      <c r="F28" t="s">
+        <v>9</v>
+      </c>
+      <c r="G28">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7">
+      <c r="A29">
+        <v>20330051920368</v>
+      </c>
+      <c r="B29" t="s">
+        <v>42</v>
+      </c>
+      <c r="C29" t="s">
+        <v>81</v>
+      </c>
+      <c r="D29" t="s">
+        <v>131</v>
+      </c>
+      <c r="E29" t="s">
+        <v>8</v>
+      </c>
+      <c r="F29" t="s">
+        <v>10</v>
+      </c>
+      <c r="G29">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7">
+      <c r="A30">
+        <v>20330051920156</v>
+      </c>
+      <c r="B30" t="s">
+        <v>43</v>
+      </c>
+      <c r="C30" t="s">
+        <v>49</v>
+      </c>
+      <c r="D30" t="s">
+        <v>132</v>
+      </c>
+      <c r="E30" t="s">
+        <v>8</v>
+      </c>
+      <c r="F30" t="s">
+        <v>10</v>
+      </c>
+      <c r="G30">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7">
+      <c r="A31">
+        <v>20330051920157</v>
+      </c>
+      <c r="B31" t="s">
+        <v>44</v>
+      </c>
+      <c r="C31" t="s">
+        <v>83</v>
+      </c>
+      <c r="D31" t="s">
+        <v>133</v>
+      </c>
+      <c r="E31" t="s">
+        <v>8</v>
+      </c>
+      <c r="F31" t="s">
+        <v>10</v>
+      </c>
+      <c r="G31">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7">
+      <c r="A32">
+        <v>20330051920369</v>
+      </c>
+      <c r="B32" t="s">
+        <v>45</v>
+      </c>
+      <c r="C32" t="s">
+        <v>84</v>
+      </c>
+      <c r="D32" t="s">
+        <v>134</v>
+      </c>
+      <c r="E32" t="s">
+        <v>8</v>
+      </c>
+      <c r="F32" t="s">
+        <v>10</v>
+      </c>
+      <c r="G32">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7">
+      <c r="A33">
+        <v>20330051920160</v>
+      </c>
+      <c r="B33" t="s">
+        <v>46</v>
+      </c>
+      <c r="C33" t="s">
+        <v>85</v>
+      </c>
+      <c r="D33" t="s">
+        <v>135</v>
+      </c>
+      <c r="E33" t="s">
+        <v>8</v>
+      </c>
+      <c r="F33" t="s">
+        <v>10</v>
+      </c>
+      <c r="G33">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7">
+      <c r="A34">
+        <v>20330051920163</v>
+      </c>
+      <c r="B34" t="s">
+        <v>23</v>
+      </c>
+      <c r="C34" t="s">
+        <v>26</v>
+      </c>
+      <c r="D34" t="s">
+        <v>136</v>
+      </c>
+      <c r="E34" t="s">
+        <v>8</v>
+      </c>
+      <c r="F34" t="s">
+        <v>10</v>
+      </c>
+      <c r="G34">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7">
+      <c r="A35">
+        <v>20330051920370</v>
+      </c>
+      <c r="B35" t="s">
+        <v>47</v>
+      </c>
+      <c r="C35" t="s">
+        <v>86</v>
+      </c>
+      <c r="D35" t="s">
+        <v>137</v>
+      </c>
+      <c r="E35" t="s">
+        <v>8</v>
+      </c>
+      <c r="F35" t="s">
+        <v>10</v>
+      </c>
+      <c r="G35">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7">
+      <c r="A36">
+        <v>20330051920372</v>
+      </c>
+      <c r="B36" t="s">
+        <v>24</v>
+      </c>
+      <c r="C36" t="s">
+        <v>87</v>
+      </c>
+      <c r="D36" t="s">
+        <v>138</v>
+      </c>
+      <c r="E36" t="s">
+        <v>8</v>
+      </c>
+      <c r="F36" t="s">
+        <v>10</v>
+      </c>
+      <c r="G36">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7">
+      <c r="A37">
+        <v>20330051920165</v>
+      </c>
+      <c r="B37" t="s">
+        <v>48</v>
+      </c>
+      <c r="C37" t="s">
         <v>88</v>
       </c>
-      <c r="E28" t="s">
-        <v>8</v>
-      </c>
-      <c r="F28" t="s">
-        <v>9</v>
-      </c>
-      <c r="G28">
+      <c r="D37" t="s">
+        <v>139</v>
+      </c>
+      <c r="E37" t="s">
+        <v>8</v>
+      </c>
+      <c r="F37" t="s">
+        <v>10</v>
+      </c>
+      <c r="G37">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7">
+      <c r="A38">
+        <v>20330051920167</v>
+      </c>
+      <c r="B38" t="s">
+        <v>26</v>
+      </c>
+      <c r="C38" t="s">
+        <v>89</v>
+      </c>
+      <c r="D38" t="s">
+        <v>140</v>
+      </c>
+      <c r="E38" t="s">
+        <v>8</v>
+      </c>
+      <c r="F38" t="s">
+        <v>10</v>
+      </c>
+      <c r="G38">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7">
+      <c r="A39">
+        <v>20330051920166</v>
+      </c>
+      <c r="B39" t="s">
+        <v>49</v>
+      </c>
+      <c r="C39" t="s">
+        <v>90</v>
+      </c>
+      <c r="D39" t="s">
+        <v>141</v>
+      </c>
+      <c r="E39" t="s">
+        <v>8</v>
+      </c>
+      <c r="F39" t="s">
+        <v>10</v>
+      </c>
+      <c r="G39">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7">
+      <c r="A40">
+        <v>20330051920168</v>
+      </c>
+      <c r="B40" t="s">
+        <v>50</v>
+      </c>
+      <c r="C40" t="s">
+        <v>25</v>
+      </c>
+      <c r="D40" t="s">
+        <v>142</v>
+      </c>
+      <c r="E40" t="s">
+        <v>8</v>
+      </c>
+      <c r="F40" t="s">
+        <v>10</v>
+      </c>
+      <c r="G40">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7">
+      <c r="A41">
+        <v>20330051920371</v>
+      </c>
+      <c r="B41" t="s">
+        <v>51</v>
+      </c>
+      <c r="C41" t="s">
+        <v>91</v>
+      </c>
+      <c r="D41" t="s">
+        <v>143</v>
+      </c>
+      <c r="E41" t="s">
+        <v>8</v>
+      </c>
+      <c r="F41" t="s">
+        <v>10</v>
+      </c>
+      <c r="G41">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7">
+      <c r="A42">
+        <v>20330051920171</v>
+      </c>
+      <c r="B42" t="s">
+        <v>52</v>
+      </c>
+      <c r="C42" t="s">
+        <v>92</v>
+      </c>
+      <c r="D42" t="s">
+        <v>144</v>
+      </c>
+      <c r="E42" t="s">
+        <v>8</v>
+      </c>
+      <c r="F42" t="s">
+        <v>10</v>
+      </c>
+      <c r="G42">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7">
+      <c r="A43">
+        <v>20330051920172</v>
+      </c>
+      <c r="B43" t="s">
+        <v>53</v>
+      </c>
+      <c r="C43" t="s">
+        <v>93</v>
+      </c>
+      <c r="D43" t="s">
+        <v>145</v>
+      </c>
+      <c r="E43" t="s">
+        <v>8</v>
+      </c>
+      <c r="F43" t="s">
+        <v>10</v>
+      </c>
+      <c r="G43">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7">
+      <c r="A44">
+        <v>20330051920306</v>
+      </c>
+      <c r="B44" t="s">
+        <v>54</v>
+      </c>
+      <c r="C44" t="s">
+        <v>24</v>
+      </c>
+      <c r="D44" t="s">
+        <v>146</v>
+      </c>
+      <c r="E44" t="s">
+        <v>8</v>
+      </c>
+      <c r="F44" t="s">
+        <v>10</v>
+      </c>
+      <c r="G44">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7">
+      <c r="A45">
+        <v>20330051920179</v>
+      </c>
+      <c r="B45" t="s">
+        <v>36</v>
+      </c>
+      <c r="C45" t="s">
+        <v>94</v>
+      </c>
+      <c r="D45" t="s">
+        <v>147</v>
+      </c>
+      <c r="E45" t="s">
+        <v>8</v>
+      </c>
+      <c r="F45" t="s">
+        <v>10</v>
+      </c>
+      <c r="G45">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7">
+      <c r="A46">
+        <v>20330051920180</v>
+      </c>
+      <c r="B46" t="s">
+        <v>55</v>
+      </c>
+      <c r="C46" t="s">
+        <v>95</v>
+      </c>
+      <c r="D46" t="s">
+        <v>148</v>
+      </c>
+      <c r="E46" t="s">
+        <v>8</v>
+      </c>
+      <c r="F46" t="s">
+        <v>10</v>
+      </c>
+      <c r="G46">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7">
+      <c r="A47">
+        <v>20330051920373</v>
+      </c>
+      <c r="B47" t="s">
+        <v>56</v>
+      </c>
+      <c r="C47" t="s">
+        <v>96</v>
+      </c>
+      <c r="D47" t="s">
+        <v>149</v>
+      </c>
+      <c r="E47" t="s">
+        <v>8</v>
+      </c>
+      <c r="F47" t="s">
+        <v>10</v>
+      </c>
+      <c r="G47">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7">
+      <c r="A48">
+        <v>20330051920254</v>
+      </c>
+      <c r="B48" t="s">
+        <v>38</v>
+      </c>
+      <c r="C48" t="s">
+        <v>64</v>
+      </c>
+      <c r="D48" t="s">
+        <v>150</v>
+      </c>
+      <c r="E48" t="s">
+        <v>8</v>
+      </c>
+      <c r="F48" t="s">
+        <v>10</v>
+      </c>
+      <c r="G48">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7">
+      <c r="A49">
+        <v>20330051920181</v>
+      </c>
+      <c r="B49" t="s">
+        <v>38</v>
+      </c>
+      <c r="C49" t="s">
+        <v>97</v>
+      </c>
+      <c r="D49" t="s">
+        <v>151</v>
+      </c>
+      <c r="E49" t="s">
+        <v>8</v>
+      </c>
+      <c r="F49" t="s">
+        <v>10</v>
+      </c>
+      <c r="G49">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7">
+      <c r="A50">
+        <v>20330051920182</v>
+      </c>
+      <c r="B50" t="s">
+        <v>57</v>
+      </c>
+      <c r="C50" t="s">
+        <v>98</v>
+      </c>
+      <c r="D50" t="s">
+        <v>120</v>
+      </c>
+      <c r="E50" t="s">
+        <v>8</v>
+      </c>
+      <c r="F50" t="s">
+        <v>10</v>
+      </c>
+      <c r="G50">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7">
+      <c r="A51">
+        <v>20330051920184</v>
+      </c>
+      <c r="B51" t="s">
+        <v>58</v>
+      </c>
+      <c r="C51" t="s">
+        <v>99</v>
+      </c>
+      <c r="D51" t="s">
+        <v>152</v>
+      </c>
+      <c r="E51" t="s">
+        <v>8</v>
+      </c>
+      <c r="F51" t="s">
+        <v>10</v>
+      </c>
+      <c r="G51">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7">
+      <c r="A52">
+        <v>20330051920154</v>
+      </c>
+      <c r="B52" t="s">
+        <v>59</v>
+      </c>
+      <c r="C52" t="s">
+        <v>76</v>
+      </c>
+      <c r="D52" t="s">
+        <v>153</v>
+      </c>
+      <c r="E52" t="s">
+        <v>8</v>
+      </c>
+      <c r="F52" t="s">
+        <v>10</v>
+      </c>
+      <c r="G52">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7">
+      <c r="A53">
+        <v>20330051920186</v>
+      </c>
+      <c r="B53" t="s">
+        <v>60</v>
+      </c>
+      <c r="C53" t="s">
+        <v>100</v>
+      </c>
+      <c r="D53" t="s">
+        <v>154</v>
+      </c>
+      <c r="E53" t="s">
+        <v>8</v>
+      </c>
+      <c r="F53" t="s">
+        <v>10</v>
+      </c>
+      <c r="G53">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7">
+      <c r="A54">
+        <v>20330051920388</v>
+      </c>
+      <c r="B54" t="s">
+        <v>61</v>
+      </c>
+      <c r="C54" t="s">
+        <v>101</v>
+      </c>
+      <c r="D54" t="s">
+        <v>155</v>
+      </c>
+      <c r="E54" t="s">
+        <v>8</v>
+      </c>
+      <c r="F54" t="s">
+        <v>10</v>
+      </c>
+      <c r="G54">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7">
+      <c r="A55">
+        <v>20330051920317</v>
+      </c>
+      <c r="B55" t="s">
+        <v>62</v>
+      </c>
+      <c r="C55" t="s">
+        <v>84</v>
+      </c>
+      <c r="D55" t="s">
+        <v>156</v>
+      </c>
+      <c r="E55" t="s">
+        <v>8</v>
+      </c>
+      <c r="F55" t="s">
+        <v>12</v>
+      </c>
+      <c r="G55">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7">
+      <c r="A56">
+        <v>20330051920322</v>
+      </c>
+      <c r="B56" t="s">
+        <v>25</v>
+      </c>
+      <c r="C56" t="s">
+        <v>24</v>
+      </c>
+      <c r="D56" t="s">
+        <v>157</v>
+      </c>
+      <c r="E56" t="s">
+        <v>8</v>
+      </c>
+      <c r="F56" t="s">
+        <v>12</v>
+      </c>
+      <c r="G56">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7">
+      <c r="A57">
+        <v>20330051920380</v>
+      </c>
+      <c r="B57" t="s">
+        <v>63</v>
+      </c>
+      <c r="C57" t="s">
+        <v>102</v>
+      </c>
+      <c r="D57" t="s">
+        <v>158</v>
+      </c>
+      <c r="E57" t="s">
+        <v>8</v>
+      </c>
+      <c r="F57" t="s">
+        <v>12</v>
+      </c>
+      <c r="G57">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7">
+      <c r="A58">
+        <v>20330051920331</v>
+      </c>
+      <c r="B58" t="s">
+        <v>64</v>
+      </c>
+      <c r="C58" t="s">
+        <v>103</v>
+      </c>
+      <c r="D58" t="s">
+        <v>159</v>
+      </c>
+      <c r="E58" t="s">
+        <v>8</v>
+      </c>
+      <c r="F58" t="s">
+        <v>12</v>
+      </c>
+      <c r="G58">
         <v>2</v>
       </c>
     </row>

--- a/docentes/Vargas Olvera Francisco Eduardo - Estadisticos 20212.xlsx
+++ b/docentes/Vargas Olvera Francisco Eduardo - Estadisticos 20212.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="26">
   <si>
     <t>Mat</t>
   </si>
@@ -82,6 +82,9 @@
     <t>XOTLANIHUA</t>
   </si>
   <si>
+    <t>RAMOS</t>
+  </si>
+  <si>
     <t>FLORES</t>
   </si>
   <si>
@@ -89,6 +92,9 @@
   </si>
   <si>
     <t>ERIKA</t>
+  </si>
+  <si>
+    <t>MARCO JOSAFAT</t>
   </si>
 </sst>
 </file>
@@ -486,10 +492,10 @@
         <v>9</v>
       </c>
       <c r="C2">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E2">
         <v>0</v>
@@ -498,7 +504,7 @@
         <v>33</v>
       </c>
       <c r="G2">
-        <v>89.19</v>
+        <v>91.67</v>
       </c>
       <c r="H2">
         <v>9</v>
@@ -515,19 +521,19 @@
         <v>36</v>
       </c>
       <c r="D3">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E3">
         <v>0</v>
       </c>
       <c r="F3">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="G3">
-        <v>94.44</v>
+        <v>100</v>
       </c>
       <c r="H3">
-        <v>8.9</v>
+        <v>8.800000000000001</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -629,19 +635,22 @@
         <v>9</v>
       </c>
       <c r="C2">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D2">
-        <v>37</v>
+        <v>3</v>
       </c>
       <c r="E2">
+        <v>0</v>
+      </c>
+      <c r="F2">
         <v>33</v>
       </c>
-      <c r="F2">
-        <v>0</v>
-      </c>
       <c r="G2">
-        <v>0</v>
+        <v>91.67</v>
+      </c>
+      <c r="H2">
+        <v>9</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -658,7 +667,7 @@
         <v>36</v>
       </c>
       <c r="E3">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="F3">
         <v>0</v>
@@ -760,10 +769,10 @@
         <v>9</v>
       </c>
       <c r="C2">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E2">
         <v>0</v>
@@ -772,10 +781,10 @@
         <v>33</v>
       </c>
       <c r="G2">
-        <v>89.19</v>
+        <v>91.67</v>
       </c>
       <c r="H2">
-        <v>9</v>
+        <v>8.9</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -789,19 +798,19 @@
         <v>36</v>
       </c>
       <c r="D3">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E3">
         <v>0</v>
       </c>
       <c r="F3">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="G3">
-        <v>94.44</v>
+        <v>100</v>
       </c>
       <c r="H3">
-        <v>8.9</v>
+        <v>8.800000000000001</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -863,7 +872,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -901,10 +910,10 @@
         <v>19</v>
       </c>
       <c r="C2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -927,7 +936,7 @@
         <v>20</v>
       </c>
       <c r="D3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -936,6 +945,29 @@
         <v>9</v>
       </c>
       <c r="G3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4">
+        <v>20330051920278</v>
+      </c>
+      <c r="B4" t="s">
+        <v>21</v>
+      </c>
+      <c r="C4" t="s">
+        <v>20</v>
+      </c>
+      <c r="D4" t="s">
+        <v>25</v>
+      </c>
+      <c r="E4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G4">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Vargas Olvera Francisco Eduardo - Estadisticos 20212.xlsx
+++ b/docentes/Vargas Olvera Francisco Eduardo - Estadisticos 20212.xlsx
@@ -76,22 +76,22 @@
     <t>Reprobadas</t>
   </si>
   <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
     <t>XOTLANIHUA</t>
   </si>
   <si>
+    <t>ORTIZ</t>
+  </si>
+  <si>
     <t>RAMOS</t>
   </si>
   <si>
-    <t>FLORES</t>
-  </si>
-  <si>
-    <t>MARCOS</t>
+    <t>SANCHEZ</t>
   </si>
   <si>
     <t>ERIKA</t>
+  </si>
+  <si>
+    <t>IRVING JAIR</t>
   </si>
   <si>
     <t>MARCO JOSAFAT</t>
@@ -573,19 +573,19 @@
         <v>19</v>
       </c>
       <c r="D5">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E5">
         <v>0</v>
       </c>
       <c r="F5">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="G5">
-        <v>73.68000000000001</v>
+        <v>84.20999999999999</v>
       </c>
       <c r="H5">
-        <v>8.4</v>
+        <v>8.1</v>
       </c>
     </row>
   </sheetData>
@@ -664,16 +664,19 @@
         <v>36</v>
       </c>
       <c r="D3">
-        <v>36</v>
+        <v>2</v>
       </c>
       <c r="E3">
-        <v>36</v>
+        <v>2</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>94.44</v>
+      </c>
+      <c r="H3">
+        <v>8.9</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -687,16 +690,19 @@
         <v>20</v>
       </c>
       <c r="D4">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="E4">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>50</v>
+      </c>
+      <c r="H4">
+        <v>7.6</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -710,16 +716,19 @@
         <v>19</v>
       </c>
       <c r="D5">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="E5">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="F5">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>68.42</v>
+      </c>
+      <c r="H5">
+        <v>8.199999999999999</v>
       </c>
     </row>
   </sheetData>
@@ -810,7 +819,7 @@
         <v>100</v>
       </c>
       <c r="H3">
-        <v>8.800000000000001</v>
+        <v>8.699999999999999</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -827,16 +836,16 @@
         <v>7</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F4">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G4">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="H4">
-        <v>7.5</v>
+        <v>7.8</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -850,19 +859,19 @@
         <v>19</v>
       </c>
       <c r="D5">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E5">
         <v>0</v>
       </c>
       <c r="F5">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="G5">
-        <v>73.68000000000001</v>
+        <v>84.20999999999999</v>
       </c>
       <c r="H5">
-        <v>8.4</v>
+        <v>8.1</v>
       </c>
     </row>
   </sheetData>
@@ -904,13 +913,13 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>20330051920322</v>
+        <v>20330051920258</v>
       </c>
       <c r="B2" t="s">
         <v>19</v>
       </c>
       <c r="C2" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="D2" t="s">
         <v>23</v>
@@ -919,21 +928,21 @@
         <v>8</v>
       </c>
       <c r="F2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="G2">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>20330051920258</v>
+        <v>19330051920238</v>
       </c>
       <c r="B3" t="s">
         <v>20</v>
       </c>
       <c r="C3" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D3" t="s">
         <v>24</v>
@@ -942,7 +951,7 @@
         <v>8</v>
       </c>
       <c r="F3" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="G3">
         <v>1</v>
@@ -956,7 +965,7 @@
         <v>21</v>
       </c>
       <c r="C4" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D4" t="s">
         <v>25</v>

--- a/docentes/Vargas Olvera Francisco Eduardo - Estadisticos 20212.xlsx
+++ b/docentes/Vargas Olvera Francisco Eduardo - Estadisticos 20212.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="41">
   <si>
     <t>Mat</t>
   </si>
@@ -76,6 +76,21 @@
     <t>Reprobadas</t>
   </si>
   <si>
+    <t>CASTRO</t>
+  </si>
+  <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
+    <t>SANTIAGO</t>
+  </si>
+  <si>
+    <t>CANTELLAN</t>
+  </si>
+  <si>
+    <t>GARCIA</t>
+  </si>
+  <si>
     <t>XOTLANIHUA</t>
   </si>
   <si>
@@ -85,7 +100,37 @@
     <t>RAMOS</t>
   </si>
   <si>
+    <t>RAMIREZ</t>
+  </si>
+  <si>
+    <t>RODRIGUEZ</t>
+  </si>
+  <si>
+    <t>REYES</t>
+  </si>
+  <si>
+    <t>LARA</t>
+  </si>
+  <si>
+    <t>FLORES</t>
+  </si>
+  <si>
     <t>SANCHEZ</t>
+  </si>
+  <si>
+    <t>JOSE ANTONIO</t>
+  </si>
+  <si>
+    <t>DANIEL ELEAZAR</t>
+  </si>
+  <si>
+    <t>AXEL YAEL</t>
+  </si>
+  <si>
+    <t>DANIELA DEL CARMEN</t>
+  </si>
+  <si>
+    <t>MARCOS</t>
   </si>
   <si>
     <t>ERIKA</t>
@@ -881,7 +926,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:G9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -913,39 +958,39 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>20330051920258</v>
+        <v>19330051920314</v>
       </c>
       <c r="B2" t="s">
         <v>19</v>
       </c>
       <c r="C2" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="D2" t="s">
-        <v>23</v>
+        <v>33</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
       </c>
       <c r="F2" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="G2">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>19330051920238</v>
+        <v>20330051920274</v>
       </c>
       <c r="B3" t="s">
         <v>20</v>
       </c>
       <c r="C3" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="D3" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -954,21 +999,21 @@
         <v>11</v>
       </c>
       <c r="G3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>20330051920278</v>
+        <v>20330051920279</v>
       </c>
       <c r="B4" t="s">
         <v>21</v>
       </c>
       <c r="C4" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="D4" t="s">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
@@ -977,6 +1022,121 @@
         <v>11</v>
       </c>
       <c r="G4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5">
+        <v>20330051920320</v>
+      </c>
+      <c r="B5" t="s">
+        <v>22</v>
+      </c>
+      <c r="C5" t="s">
+        <v>30</v>
+      </c>
+      <c r="D5" t="s">
+        <v>36</v>
+      </c>
+      <c r="E5" t="s">
+        <v>8</v>
+      </c>
+      <c r="F5" t="s">
+        <v>12</v>
+      </c>
+      <c r="G5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6">
+        <v>20330051920322</v>
+      </c>
+      <c r="B6" t="s">
+        <v>23</v>
+      </c>
+      <c r="C6" t="s">
+        <v>31</v>
+      </c>
+      <c r="D6" t="s">
+        <v>37</v>
+      </c>
+      <c r="E6" t="s">
+        <v>8</v>
+      </c>
+      <c r="F6" t="s">
+        <v>12</v>
+      </c>
+      <c r="G6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7">
+        <v>20330051920258</v>
+      </c>
+      <c r="B7" t="s">
+        <v>24</v>
+      </c>
+      <c r="C7" t="s">
+        <v>24</v>
+      </c>
+      <c r="D7" t="s">
+        <v>38</v>
+      </c>
+      <c r="E7" t="s">
+        <v>8</v>
+      </c>
+      <c r="F7" t="s">
+        <v>9</v>
+      </c>
+      <c r="G7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="A8">
+        <v>19330051920238</v>
+      </c>
+      <c r="B8" t="s">
+        <v>25</v>
+      </c>
+      <c r="C8" t="s">
+        <v>32</v>
+      </c>
+      <c r="D8" t="s">
+        <v>39</v>
+      </c>
+      <c r="E8" t="s">
+        <v>8</v>
+      </c>
+      <c r="F8" t="s">
+        <v>11</v>
+      </c>
+      <c r="G8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9">
+        <v>20330051920278</v>
+      </c>
+      <c r="B9" t="s">
+        <v>26</v>
+      </c>
+      <c r="C9" t="s">
+        <v>24</v>
+      </c>
+      <c r="D9" t="s">
+        <v>40</v>
+      </c>
+      <c r="E9" t="s">
+        <v>8</v>
+      </c>
+      <c r="F9" t="s">
+        <v>11</v>
+      </c>
+      <c r="G9">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Vargas Olvera Francisco Eduardo - Estadisticos 20212.xlsx
+++ b/docentes/Vargas Olvera Francisco Eduardo - Estadisticos 20212.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="25">
   <si>
     <t>Mat</t>
   </si>
@@ -76,70 +76,22 @@
     <t>Reprobadas</t>
   </si>
   <si>
-    <t>CASTRO</t>
-  </si>
-  <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
     <t>SANTIAGO</t>
   </si>
   <si>
-    <t>CANTELLAN</t>
-  </si>
-  <si>
     <t>GARCIA</t>
   </si>
   <si>
-    <t>XOTLANIHUA</t>
-  </si>
-  <si>
-    <t>ORTIZ</t>
-  </si>
-  <si>
-    <t>RAMOS</t>
-  </si>
-  <si>
-    <t>RAMIREZ</t>
-  </si>
-  <si>
-    <t>RODRIGUEZ</t>
-  </si>
-  <si>
     <t>REYES</t>
   </si>
   <si>
-    <t>LARA</t>
-  </si>
-  <si>
     <t>FLORES</t>
   </si>
   <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
-    <t>JOSE ANTONIO</t>
-  </si>
-  <si>
-    <t>DANIEL ELEAZAR</t>
-  </si>
-  <si>
     <t>AXEL YAEL</t>
   </si>
   <si>
-    <t>DANIELA DEL CARMEN</t>
-  </si>
-  <si>
     <t>MARCOS</t>
-  </si>
-  <si>
-    <t>ERIKA</t>
-  </si>
-  <si>
-    <t>IRVING JAIR</t>
-  </si>
-  <si>
-    <t>MARCO JOSAFAT</t>
   </si>
 </sst>
 </file>
@@ -540,16 +492,16 @@
         <v>36</v>
       </c>
       <c r="D2">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E2">
         <v>0</v>
       </c>
       <c r="F2">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="G2">
-        <v>91.67</v>
+        <v>100</v>
       </c>
       <c r="H2">
         <v>9</v>
@@ -592,19 +544,19 @@
         <v>20</v>
       </c>
       <c r="D4">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F4">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G4">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="H4">
-        <v>7.5</v>
+        <v>6.8</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -618,19 +570,19 @@
         <v>19</v>
       </c>
       <c r="D5">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F5">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G5">
-        <v>84.20999999999999</v>
+        <v>89.47</v>
       </c>
       <c r="H5">
-        <v>8.1</v>
+        <v>7.8</v>
       </c>
     </row>
   </sheetData>
@@ -683,16 +635,16 @@
         <v>36</v>
       </c>
       <c r="D2">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E2">
         <v>0</v>
       </c>
       <c r="F2">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="G2">
-        <v>91.67</v>
+        <v>100</v>
       </c>
       <c r="H2">
         <v>9</v>
@@ -709,19 +661,19 @@
         <v>36</v>
       </c>
       <c r="D3">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F3">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="G3">
-        <v>94.44</v>
+        <v>100</v>
       </c>
       <c r="H3">
-        <v>8.9</v>
+        <v>8.800000000000001</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -735,19 +687,19 @@
         <v>20</v>
       </c>
       <c r="D4">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="E4">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="F4">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="G4">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="H4">
-        <v>7.6</v>
+        <v>6.8</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -761,19 +713,19 @@
         <v>19</v>
       </c>
       <c r="D5">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="E5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F5">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="G5">
-        <v>68.42</v>
+        <v>89.47</v>
       </c>
       <c r="H5">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
     </row>
   </sheetData>
@@ -826,19 +778,19 @@
         <v>36</v>
       </c>
       <c r="D2">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E2">
         <v>0</v>
       </c>
       <c r="F2">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="G2">
-        <v>91.67</v>
+        <v>100</v>
       </c>
       <c r="H2">
-        <v>8.9</v>
+        <v>8.6</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -864,7 +816,7 @@
         <v>100</v>
       </c>
       <c r="H3">
-        <v>8.699999999999999</v>
+        <v>8.800000000000001</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -878,19 +830,19 @@
         <v>20</v>
       </c>
       <c r="D4">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="E4">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F4">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="G4">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="H4">
-        <v>7.8</v>
+        <v>6.8</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -904,19 +856,19 @@
         <v>19</v>
       </c>
       <c r="D5">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F5">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G5">
-        <v>84.20999999999999</v>
+        <v>89.47</v>
       </c>
       <c r="H5">
-        <v>8.1</v>
+        <v>7.4</v>
       </c>
     </row>
   </sheetData>
@@ -926,7 +878,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:G3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -958,16 +910,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>19330051920314</v>
+        <v>20330051920279</v>
       </c>
       <c r="B2" t="s">
         <v>19</v>
       </c>
       <c r="C2" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="D2" t="s">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -981,162 +933,24 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>20330051920274</v>
+        <v>20330051920322</v>
       </c>
       <c r="B3" t="s">
         <v>20</v>
       </c>
       <c r="C3" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="D3" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
       </c>
       <c r="F3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
-      <c r="A4">
-        <v>20330051920279</v>
-      </c>
-      <c r="B4" t="s">
-        <v>21</v>
-      </c>
-      <c r="C4" t="s">
-        <v>29</v>
-      </c>
-      <c r="D4" t="s">
-        <v>35</v>
-      </c>
-      <c r="E4" t="s">
-        <v>8</v>
-      </c>
-      <c r="F4" t="s">
-        <v>11</v>
-      </c>
-      <c r="G4">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
-      <c r="A5">
-        <v>20330051920320</v>
-      </c>
-      <c r="B5" t="s">
-        <v>22</v>
-      </c>
-      <c r="C5" t="s">
-        <v>30</v>
-      </c>
-      <c r="D5" t="s">
-        <v>36</v>
-      </c>
-      <c r="E5" t="s">
-        <v>8</v>
-      </c>
-      <c r="F5" t="s">
-        <v>12</v>
-      </c>
-      <c r="G5">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6">
-        <v>20330051920322</v>
-      </c>
-      <c r="B6" t="s">
-        <v>23</v>
-      </c>
-      <c r="C6" t="s">
-        <v>31</v>
-      </c>
-      <c r="D6" t="s">
-        <v>37</v>
-      </c>
-      <c r="E6" t="s">
-        <v>8</v>
-      </c>
-      <c r="F6" t="s">
-        <v>12</v>
-      </c>
-      <c r="G6">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="A7">
-        <v>20330051920258</v>
-      </c>
-      <c r="B7" t="s">
-        <v>24</v>
-      </c>
-      <c r="C7" t="s">
-        <v>24</v>
-      </c>
-      <c r="D7" t="s">
-        <v>38</v>
-      </c>
-      <c r="E7" t="s">
-        <v>8</v>
-      </c>
-      <c r="F7" t="s">
-        <v>9</v>
-      </c>
-      <c r="G7">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="A8">
-        <v>19330051920238</v>
-      </c>
-      <c r="B8" t="s">
-        <v>25</v>
-      </c>
-      <c r="C8" t="s">
-        <v>32</v>
-      </c>
-      <c r="D8" t="s">
-        <v>39</v>
-      </c>
-      <c r="E8" t="s">
-        <v>8</v>
-      </c>
-      <c r="F8" t="s">
-        <v>11</v>
-      </c>
-      <c r="G8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9">
-        <v>20330051920278</v>
-      </c>
-      <c r="B9" t="s">
-        <v>26</v>
-      </c>
-      <c r="C9" t="s">
-        <v>24</v>
-      </c>
-      <c r="D9" t="s">
-        <v>40</v>
-      </c>
-      <c r="E9" t="s">
-        <v>8</v>
-      </c>
-      <c r="F9" t="s">
-        <v>11</v>
-      </c>
-      <c r="G9">
         <v>1</v>
       </c>
     </row>
